--- a/excel/intake_twohigh.xlsx
+++ b/excel/intake_twohigh.xlsx
@@ -584,7 +584,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -890,7 +889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -963,25 +962,30 @@
       </c>
       <c r="K1" s="18" t="inlineStr">
         <is>
+          <t>ct_differential</t>
+        </is>
+      </c>
+      <c r="L1" s="18" t="inlineStr">
+        <is>
           <t>ct_metering</t>
         </is>
       </c>
-      <c r="L1" s="18" t="inlineStr">
+      <c r="M1" s="18" t="inlineStr">
         <is>
           <t>ct_ground</t>
         </is>
       </c>
-      <c r="M1" s="18" t="inlineStr">
+      <c r="N1" s="18" t="inlineStr">
         <is>
           <t>pt</t>
         </is>
       </c>
-      <c r="N1" s="18" t="inlineStr">
+      <c r="O1" s="18" t="inlineStr">
         <is>
           <t>pt_primary_fuse</t>
         </is>
       </c>
-      <c r="O1" s="18" t="inlineStr">
+      <c r="P1" s="18" t="inlineStr">
         <is>
           <t>destination</t>
         </is>
@@ -1040,7 +1044,8 @@
       <c r="L2" s="19" t="n"/>
       <c r="M2" s="19" t="n"/>
       <c r="N2" s="19" t="n"/>
-      <c r="O2" s="19" t="inlineStr">
+      <c r="O2" s="19" t="n"/>
+      <c r="P2" s="19" t="inlineStr">
         <is>
           <t>UTILITY SUPPLY 13.8kV, 3PH, 60HZ</t>
         </is>
@@ -1073,17 +1078,18 @@
       <c r="J3" s="19" t="n"/>
       <c r="K3" s="19" t="n"/>
       <c r="L3" s="19" t="n"/>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="M3" s="19" t="n"/>
+      <c r="N3" s="19" t="inlineStr">
         <is>
           <t>14,400:120V</t>
         </is>
       </c>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="O3" s="19" t="inlineStr">
         <is>
           <t>CLF 0.5E</t>
         </is>
       </c>
-      <c r="O3" s="19" t="n"/>
+      <c r="P3" s="19" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="19" t="n">
@@ -1138,7 +1144,8 @@
       <c r="L4" s="19" t="n"/>
       <c r="M4" s="19" t="n"/>
       <c r="N4" s="19" t="n"/>
-      <c r="O4" s="19" t="inlineStr">
+      <c r="O4" s="19" t="n"/>
+      <c r="P4" s="19" t="inlineStr">
         <is>
           <t>TO 2500kVA XFMR 13.8kV-480Y/277V</t>
         </is>
@@ -1194,14 +1201,15 @@
         </is>
       </c>
       <c r="K5" s="19" t="n"/>
-      <c r="L5" s="19" t="inlineStr">
+      <c r="L5" s="19" t="n"/>
+      <c r="M5" s="19" t="inlineStr">
         <is>
           <t>50:5A</t>
         </is>
       </c>
-      <c r="M5" s="19" t="n"/>
       <c r="N5" s="19" t="n"/>
-      <c r="O5" s="19" t="inlineStr">
+      <c r="O5" s="19" t="n"/>
+      <c r="P5" s="19" t="inlineStr">
         <is>
           <t>TO 1500HP 13.8kV MOTOR</t>
         </is>
@@ -1256,11 +1264,16 @@
           <t>400:5A (3)</t>
         </is>
       </c>
-      <c r="K6" s="19" t="n"/>
+      <c r="K6" s="19" t="inlineStr">
+        <is>
+          <t>400:5A (3)</t>
+        </is>
+      </c>
       <c r="L6" s="19" t="n"/>
       <c r="M6" s="19" t="n"/>
       <c r="N6" s="19" t="n"/>
-      <c r="O6" s="19" t="inlineStr">
+      <c r="O6" s="19" t="n"/>
+      <c r="P6" s="19" t="inlineStr">
         <is>
           <t>RESERVED FOR FUTURE REQUIREMENT</t>
         </is>

--- a/excel/intake_twohigh.xlsx
+++ b/excel/intake_twohigh.xlsx
@@ -1201,12 +1201,12 @@
         </is>
       </c>
       <c r="K5" s="19" t="n"/>
-      <c r="L5" s="19" t="n"/>
-      <c r="M5" s="19" t="inlineStr">
-        <is>
-          <t>50:5A</t>
-        </is>
-      </c>
+      <c r="L5" s="19" t="inlineStr">
+        <is>
+          <t>2000:5A (3)</t>
+        </is>
+      </c>
+      <c r="M5" s="19" t="n"/>
       <c r="N5" s="19" t="n"/>
       <c r="O5" s="19" t="n"/>
       <c r="P5" s="19" t="inlineStr">
